--- a/Configs/GameConfig/Datas/fg/#IntelBoss-首领弱点情报.xlsx
+++ b/Configs/GameConfig/Datas/fg/#IntelBoss-首领弱点情报.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,6 +576,42 @@
       </c>
       <c r="H4" t="n">
         <v>10</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>silent_mind</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>intel.boss.silent_mind.name</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>silent_mind</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>intel.boss.silent_mind.phases</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>intel.boss.silent_mind.weakness</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>intel.boss.silent_mind.advice</t>
+        </is>
+      </c>
+      <c r="H5" t="n">
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Configs/GameConfig/Datas/fg/#IntelBoss-首领弱点情报.xlsx
+++ b/Configs/GameConfig/Datas/fg/#IntelBoss-首领弱点情报.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -612,6 +612,42 @@
       </c>
       <c r="H5" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>baptism_tower</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>intel.boss.baptism_tower.name</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>baptism_tower</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>intel.boss.baptism_tower.phases</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>intel.boss.baptism_tower.weakness</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>intel.boss.baptism_tower.advice</t>
+        </is>
+      </c>
+      <c r="H6" t="n">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
